--- a/utils/monday_sprint_sprint_2024-50.xlsx
+++ b/utils/monday_sprint_sprint_2024-50.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="188">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>28159</t>
+    <t>7618681726</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>11/10/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>08/12/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -111,16 +111,16 @@
     <t>11/11/2024</t>
   </si>
   <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Novembro</t>
   </si>
   <si>
-    <t>28152</t>
+    <t>7911853526</t>
   </si>
   <si>
     <t>Sistema Horas</t>
@@ -129,25 +129,25 @@
     <t>22/11/2024</t>
   </si>
   <si>
+    <t>26/11/2024</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>7920932372</t>
   </si>
   <si>
     <t>Ajuste no sistema BLOCO K</t>
   </si>
   <si>
-    <t>25/11/2024</t>
-  </si>
-  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>24822</t>
+    <t>6348301142</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) APOIO por Sub-área</t>
@@ -159,7 +159,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>28063</t>
+    <t>7911873140</t>
   </si>
   <si>
     <t>Correção</t>
@@ -168,7 +168,10 @@
     <t>Peças UPR &gt; Avaliação Ronda</t>
   </si>
   <si>
-    <t>28586</t>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>7920843757</t>
   </si>
   <si>
     <t>Apontamentos Manipulador Rebarbação VI</t>
@@ -177,7 +180,10 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>24821</t>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>8754783359</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) Usinagem por Sub-área (copy)</t>
@@ -186,121 +192,133 @@
     <t>21/03/2025</t>
   </si>
   <si>
+    <t>27/11/2024</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
-    <t>28379</t>
+    <t>7920843801</t>
   </si>
   <si>
     <t>Apontamento Horímetro Deltractor</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>7823643514</t>
   </si>
   <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Manutenção dos dados importados (copy)</t>
   </si>
   <si>
-    <t>28751</t>
+    <t>7925366224</t>
   </si>
   <si>
     <t>Apontamentos Acabamento USE OUT/2024</t>
   </si>
   <si>
-    <t>28846</t>
+    <t>7911617714</t>
   </si>
   <si>
     <t>Eliminar itens da lista</t>
   </si>
   <si>
-    <t>26390</t>
+    <t>03/12/2024</t>
+  </si>
+  <si>
+    <t>7911881858</t>
   </si>
   <si>
     <t>Alteração apontamento ajustagem</t>
   </si>
   <si>
-    <t>28100</t>
+    <t>7921427062</t>
   </si>
   <si>
     <t>Qlik Sense - Dados</t>
   </si>
   <si>
-    <t>28895</t>
+    <t>7926225289</t>
   </si>
   <si>
     <t>Plano de ação GPT Jr. 01</t>
   </si>
   <si>
-    <t>26814</t>
+    <t>7926200402</t>
   </si>
   <si>
     <t>ERRO INVENTÁRIO GERAL</t>
   </si>
   <si>
-    <t>28785</t>
+    <t>7911714758</t>
   </si>
   <si>
     <t>Fiedler X ALTONA 2.0</t>
   </si>
   <si>
-    <t>28796</t>
+    <t>02/12/2024</t>
+  </si>
+  <si>
+    <t>7911700784</t>
   </si>
   <si>
     <t>Melhoria sistema de corrida</t>
   </si>
   <si>
-    <t>28106</t>
+    <t>7921421070</t>
   </si>
   <si>
     <t>Qlik Sense - Dados CTe</t>
   </si>
   <si>
-    <t>28774</t>
+    <t>7911823148</t>
   </si>
   <si>
     <t>Erro Sequência ZZZZZ</t>
   </si>
   <si>
-    <t>28761</t>
+    <t>7911728764</t>
   </si>
   <si>
     <t>Definir quais usuários podem alterar pré-lista</t>
   </si>
   <si>
-    <t>28797</t>
+    <t>28/11/2024</t>
+  </si>
+  <si>
+    <t>7911679622</t>
   </si>
   <si>
     <t>NOVO CAMPO PENDÊNCIAS</t>
   </si>
   <si>
-    <t>28281</t>
+    <t>7911841231</t>
   </si>
   <si>
     <t>Falta Informação relatório</t>
   </si>
   <si>
-    <t>28819</t>
+    <t>7911778261</t>
   </si>
   <si>
     <t>Razão Crítica - Validação</t>
   </si>
   <si>
-    <t>28867</t>
+    <t>7921448159</t>
+  </si>
+  <si>
+    <t>7921886138</t>
   </si>
   <si>
     <t>Custeio Beneficiamento de Terceiros OUT/2024</t>
   </si>
   <si>
-    <t>28752</t>
+    <t>7930800495</t>
   </si>
   <si>
     <t>ERRO: Custo de Entrada Materiais -  ELETRODO DE SOLDA</t>
   </si>
   <si>
-    <t>26/11/2024</t>
-  </si>
-  <si>
-    <t>29067</t>
+    <t>7981710295</t>
   </si>
   <si>
     <t>ERRO: Apontamento Acabamento USE NOV/2024</t>
@@ -315,22 +333,28 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>29048</t>
+    <t>7981790730</t>
   </si>
   <si>
     <t>Beneficiamento de Aguas Azuis Altona Eng. para Altona</t>
   </si>
   <si>
-    <t>27474</t>
+    <t>7921953549</t>
   </si>
   <si>
     <t>Função “Marcar todos” “Desmarcar todos</t>
   </si>
   <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>7921951692</t>
+  </si>
+  <si>
     <t>"Associação de grupos/cargos por “caixas de marcação”</t>
   </si>
   <si>
-    <t>27746</t>
+    <t>7428249950</t>
   </si>
   <si>
     <t>Relatório de Recibo de Embarque - Vinculo NF x Sequencia</t>
@@ -339,10 +363,13 @@
     <t>13/09/2024</t>
   </si>
   <si>
+    <t>01/12/2024</t>
+  </si>
+  <si>
     <t>Setembro</t>
   </si>
   <si>
-    <t>28410</t>
+    <t>7714903047</t>
   </si>
   <si>
     <t>ENDEREÇAMENTO ALMOXARIFADO</t>
@@ -351,10 +378,13 @@
     <t>25/10/2024</t>
   </si>
   <si>
+    <t>7921957563</t>
+  </si>
+  <si>
     <t>Separados por áreas(Semelhante ao ISODOC</t>
   </si>
   <si>
-    <t>28847</t>
+    <t>7926007813</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -363,82 +393,100 @@
     <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
   </si>
   <si>
-    <t>26964</t>
+    <t>7921949040</t>
   </si>
   <si>
     <t>Executar chamado para criação de indicadores de controle de leitura de documentos</t>
   </si>
   <si>
-    <t>28800</t>
+    <t>7911638434</t>
   </si>
   <si>
     <t>INCLUSÃO DE OTFs PARCIAIS</t>
   </si>
   <si>
-    <t>28686</t>
+    <t>7921270125</t>
   </si>
   <si>
     <t>Ciclo de indicadores com Ano comercial</t>
   </si>
   <si>
+    <t>7921262563</t>
+  </si>
+  <si>
     <t>Consulta de indicadores sem plano de ação cadastrado, com opção de disparar e-mail para os responsáveis</t>
   </si>
   <si>
-    <t>28135</t>
+    <t>7921691615</t>
   </si>
   <si>
     <t>Apontamento de moldagem USE - Máquina</t>
   </si>
   <si>
-    <t>28798</t>
+    <t>7911668621</t>
   </si>
   <si>
     <t>Cenário Valorização 2</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>7921698559</t>
   </si>
   <si>
     <t>Controle de Eventos Financeiros - Verificar cobrança conforme alocação</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>7921708547</t>
   </si>
   <si>
     <t>Vendas – Motorista identifica pela Ordem de Coleta</t>
   </si>
   <si>
+    <t>7921708313</t>
+  </si>
+  <si>
     <t>Ordem de Coleta e Entrega (Controle de Pátio)</t>
   </si>
   <si>
+    <t>7921708488</t>
+  </si>
+  <si>
     <t>Compras - Identificação pela Ordem de Compra</t>
   </si>
   <si>
+    <t>7921708598</t>
+  </si>
+  <si>
     <t>Criar tela de gestão entre logística e expedição</t>
   </si>
   <si>
+    <t>7921947183</t>
+  </si>
+  <si>
     <t>Indicar com setas e botões para mudar de página.</t>
   </si>
   <si>
-    <t>28316</t>
+    <t>7921820891</t>
   </si>
   <si>
     <t>Movimentação da montagem do conjunto das Tampas</t>
   </si>
   <si>
+    <t>7935045688</t>
+  </si>
+  <si>
     <t>Geração dos registros K230 e K235</t>
   </si>
   <si>
-    <t>29001</t>
+    <t>7947180850</t>
   </si>
   <si>
     <t>ERRO SALDO 108892/93</t>
   </si>
   <si>
-    <t>28/11/2024</t>
-  </si>
-  <si>
-    <t>27715</t>
+    <t>7926176279</t>
+  </si>
+  <si>
+    <t>7428418825</t>
   </si>
   <si>
     <t>Qlik Sense Programa 5S - Criação de novo gráfico</t>
@@ -450,7 +498,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-50</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1089,13 +1137,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1136,16 +1184,16 @@
         <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>34</v>
@@ -1153,7 +1201,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1165,10 +1213,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1180,19 +1228,19 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>34</v>
@@ -1230,16 +1278,16 @@
         <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>47</v>
@@ -1277,7 +1325,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1286,7 +1334,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>34</v>
@@ -1294,7 +1342,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1306,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1321,10 +1369,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1333,7 +1381,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>34</v>
@@ -1341,7 +1389,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1353,10 +1401,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1368,19 +1416,19 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>47</v>
@@ -1388,7 +1436,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1400,13 +1448,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1415,10 +1463,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1427,7 +1475,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>34</v>
@@ -1435,7 +1483,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1447,10 +1495,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1465,7 +1513,7 @@
         <v>31</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1482,7 +1530,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1494,10 +1542,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1509,10 +1557,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1521,7 +1569,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>34</v>
@@ -1529,7 +1577,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1541,10 +1589,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1559,7 +1607,7 @@
         <v>37</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1568,7 +1616,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>34</v>
@@ -1576,7 +1624,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1588,10 +1636,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1606,7 +1654,7 @@
         <v>37</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1615,7 +1663,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>34</v>
@@ -1623,7 +1671,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1635,10 +1683,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1650,10 +1698,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1662,7 +1710,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>34</v>
@@ -1670,7 +1718,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1682,10 +1730,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1697,7 +1745,7 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1709,7 +1757,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>34</v>
@@ -1717,7 +1765,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1729,10 +1777,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1744,10 +1792,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1756,7 +1804,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>34</v>
@@ -1764,7 +1812,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1776,10 +1824,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1794,7 +1842,7 @@
         <v>37</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1803,7 +1851,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>34</v>
@@ -1811,7 +1859,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1823,10 +1871,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1841,7 +1889,7 @@
         <v>37</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1850,7 +1898,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>34</v>
@@ -1858,7 +1906,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1870,10 +1918,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1885,10 +1933,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1897,7 +1945,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>34</v>
@@ -1905,7 +1953,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1917,10 +1965,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1935,7 +1983,7 @@
         <v>37</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1944,7 +1992,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>34</v>
@@ -1952,7 +2000,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1964,10 +2012,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1982,7 +2030,7 @@
         <v>37</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1991,7 +2039,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>34</v>
@@ -1999,7 +2047,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2011,10 +2059,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2029,7 +2077,7 @@
         <v>37</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2038,7 +2086,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>34</v>
@@ -2046,7 +2094,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2058,10 +2106,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2076,7 +2124,7 @@
         <v>37</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2085,7 +2133,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>34</v>
@@ -2093,7 +2141,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2105,10 +2153,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2123,7 +2171,7 @@
         <v>37</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2132,7 +2180,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>34</v>
@@ -2140,7 +2188,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2152,25 +2200,25 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2179,7 +2227,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>34</v>
@@ -2187,7 +2235,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2199,10 +2247,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2214,10 +2262,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2226,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>34</v>
@@ -2234,7 +2282,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2246,10 +2294,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2261,10 +2309,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2273,7 +2321,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>34</v>
@@ -2281,7 +2329,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2293,10 +2341,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2308,10 +2356,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2320,15 +2368,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2340,10 +2388,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2355,10 +2403,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2367,15 +2415,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2387,10 +2435,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2402,10 +2450,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2414,7 +2462,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>34</v>
@@ -2422,7 +2470,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2434,10 +2482,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2449,10 +2497,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2461,7 +2509,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>34</v>
@@ -2469,7 +2517,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2481,10 +2529,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2496,13 +2544,13 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
@@ -2511,12 +2559,12 @@
         <v>27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2528,10 +2576,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2543,19 +2591,19 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2563,7 +2611,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2575,10 +2623,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2590,10 +2638,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2602,7 +2650,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>34</v>
@@ -2610,22 +2658,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2637,10 +2685,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2649,7 +2697,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>34</v>
@@ -2657,7 +2705,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2669,10 +2717,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2684,19 +2732,19 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>34</v>
@@ -2704,7 +2752,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2716,10 +2764,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2734,16 +2782,16 @@
         <v>37</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>34</v>
@@ -2751,7 +2799,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2763,10 +2811,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2778,19 +2826,19 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>34</v>
@@ -2798,7 +2846,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2810,10 +2858,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2825,7 +2873,7 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -2837,7 +2885,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>34</v>
@@ -2845,7 +2893,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2857,13 +2905,13 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>21</v>
@@ -2872,7 +2920,7 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
@@ -2884,7 +2932,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>34</v>
@@ -2892,7 +2940,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2904,10 +2952,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2922,16 +2970,16 @@
         <v>37</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>34</v>
@@ -2939,22 +2987,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2966,10 +3014,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2978,7 +3026,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>34</v>
@@ -2986,7 +3034,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2998,10 +3046,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3013,10 +3061,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3025,7 +3073,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>34</v>
@@ -3033,7 +3081,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3045,10 +3093,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3060,10 +3108,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3072,7 +3120,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>34</v>
@@ -3080,7 +3128,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3092,10 +3140,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3107,10 +3155,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3119,7 +3167,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>34</v>
@@ -3127,7 +3175,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3139,10 +3187,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3154,10 +3202,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3166,7 +3214,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>34</v>
@@ -3174,7 +3222,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3186,10 +3234,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3201,19 +3249,19 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>34</v>
@@ -3221,7 +3269,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3233,10 +3281,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3248,19 +3296,19 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>34</v>
@@ -3268,7 +3316,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3280,10 +3328,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3295,10 +3343,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3307,7 +3355,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>34</v>
@@ -3315,7 +3363,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3327,10 +3375,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3342,19 +3390,19 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>34</v>
@@ -3362,7 +3410,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3374,10 +3422,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3389,19 +3437,19 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>34</v>
@@ -3409,7 +3457,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3421,10 +3469,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3436,22 +3484,22 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3467,23 +3515,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3491,16 +3539,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3511,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>14.76</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3519,7 +3567,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3532,7 +3580,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23">
         <v>2</v>
@@ -3540,7 +3588,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3571,12 +3619,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B2">
         <v>52</v>
@@ -3590,7 +3638,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3600,25 +3648,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3635,13 +3683,13 @@
         <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3653,10 +3701,10 @@
         <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3667,7 +3715,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -3676,10 +3724,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11">
         <v>9</v>
@@ -3688,12 +3736,12 @@
         <v>27</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3705,27 +3753,27 @@
         <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="K12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="Q12">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3736,16 +3784,22 @@
       <c r="N13">
         <v>5</v>
       </c>
+      <c r="P13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -3753,7 +3807,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3761,7 +3815,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3769,7 +3823,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3777,10 +3831,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3788,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3796,142 +3850,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
